--- a/docs/bobot_kesulitan_modul_fprs_v2.xlsx
+++ b/docs/bobot_kesulitan_modul_fprs_v2.xlsx
@@ -334,7 +334,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -367,7 +367,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,6 +410,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -438,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -452,7 +458,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -464,7 +470,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -474,21 +480,21 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -497,8 +503,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -508,10 +512,25 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -853,184 +872,184 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="24">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="26">
-        <v>2</v>
-      </c>
-      <c r="E2" s="27">
+      <c r="D2" s="24">
+        <v>2</v>
+      </c>
+      <c r="E2" s="25">
         <v>46225</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="25">
         <v>46230</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <v>4</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
-        <v>2</v>
-      </c>
-      <c r="B3" s="24" t="s">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="26">
-        <v>2</v>
-      </c>
-      <c r="E3" s="27">
+      <c r="D3" s="24">
+        <v>2</v>
+      </c>
+      <c r="E3" s="25">
         <v>46231</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="25">
         <v>46234</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>4</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="23" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24">
-        <v>3</v>
-      </c>
-      <c r="B4" s="24" t="s">
+    <row r="4" spans="1:8" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="26">
-        <v>1</v>
-      </c>
-      <c r="E4" s="27">
+      <c r="D4" s="24">
+        <v>1</v>
+      </c>
+      <c r="E4" s="25">
         <v>46237</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="25">
         <v>46238</v>
       </c>
-      <c r="G4" s="24">
-        <v>2</v>
-      </c>
-      <c r="H4" s="25" t="s">
+      <c r="G4" s="22">
+        <v>2</v>
+      </c>
+      <c r="H4" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+    <row r="5" spans="1:8" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="26">
-        <v>1</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="D5" s="24">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25">
         <v>46239</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="25">
         <v>46240</v>
       </c>
-      <c r="G5" s="24">
-        <v>2</v>
-      </c>
-      <c r="H5" s="25" t="s">
+      <c r="G5" s="22">
+        <v>2</v>
+      </c>
+      <c r="H5" s="23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+    <row r="6" spans="1:8" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="26">
-        <v>1</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="25">
         <v>46241</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="25">
         <v>46244</v>
       </c>
-      <c r="G6" s="24">
-        <v>2</v>
-      </c>
-      <c r="H6" s="25" t="s">
+      <c r="G6" s="22">
+        <v>2</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+    <row r="7" spans="1:8" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="26">
-        <v>1</v>
-      </c>
-      <c r="E7" s="27">
+      <c r="D7" s="24">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25">
         <v>46245</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="25">
         <v>46246</v>
       </c>
-      <c r="G7" s="24">
-        <v>2</v>
-      </c>
-      <c r="H7" s="25" t="s">
+      <c r="G7" s="22">
+        <v>2</v>
+      </c>
+      <c r="H7" s="23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+    <row r="8" spans="1:8" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="26">
-        <v>2</v>
-      </c>
-      <c r="E8" s="27">
+      <c r="D8" s="24">
+        <v>2</v>
+      </c>
+      <c r="E8" s="25">
         <v>46247</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="25">
         <v>46253</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <v>4</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="23" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1045,7 +1064,7 @@
         <v>23</v>
       </c>
       <c r="D9" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="5">
         <v>46254</v>
@@ -1060,29 +1079,29 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:8" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4">
-        <v>3</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="31">
+        <v>0</v>
+      </c>
+      <c r="E10" s="32">
         <v>46268</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="32">
         <v>46275</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="29">
         <v>6</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="30" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1097,7 +1116,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5">
         <v>46276</v>
@@ -1123,7 +1142,7 @@
         <v>29</v>
       </c>
       <c r="D12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5">
         <v>46282</v>
@@ -2699,14 +2718,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2836,12 +2855,12 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
@@ -2849,54 +2868,54 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/docs/bobot_kesulitan_modul_fprs_v2.xlsx
+++ b/docs/bobot_kesulitan_modul_fprs_v2.xlsx
@@ -516,8 +516,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,6 +529,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1079,29 +1079,29 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29">
+    <row r="10" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
         <v>9</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="29">
         <v>0</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="30">
         <v>46268</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="30">
         <v>46275</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="27">
         <v>6</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="28" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2718,14 +2718,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2855,12 +2855,12 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
@@ -2868,54 +2868,54 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="7">
